--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367579E3-9D62-42FF-A26E-0A782F682E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A27D3E-8A91-45D7-AB98-87FC910E1120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Bejelentkezés</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Dokumentáció</t>
-  </si>
-  <si>
-    <t>PPT</t>
   </si>
   <si>
     <t>PHP</t>
@@ -192,7 +189,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -200,6 +196,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -571,8 +568,8 @@
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -589,83 +586,83 @@
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="10"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="10"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
@@ -674,16 +671,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -693,17 +690,17 @@
       <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="9"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -712,15 +709,13 @@
       <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
+      <c r="B10" s="12"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
     </row>
     <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.2">
       <c r="J15" s="8"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A27D3E-8A91-45D7-AB98-87FC910E1120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D593A5F-8A4F-417F-891B-EAC68DFA0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
+    <workbookView xWindow="5970" yWindow="2250" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt-diagram" sheetId="2" r:id="rId1"/>
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -181,9 +181,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -580,23 +577,23 @@
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -607,28 +604,28 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
     </row>
     <row r="6" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -639,12 +636,12 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
@@ -653,16 +650,16 @@
         <v>11</v>
       </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="15"/>
+      <c r="D7" s="14"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
@@ -671,16 +668,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -690,17 +687,17 @@
       <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="9"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -709,13 +706,13 @@
       <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B10" s="12"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
+      <c r="B10" s="11"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
     </row>
     <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.2">
       <c r="J15" s="8"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D593A5F-8A4F-417F-891B-EAC68DFA0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3080E4-7E90-4C18-B82E-3612E2D06202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5970" yWindow="2250" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,13 +112,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -192,8 +185,8 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -632,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3080E4-7E90-4C18-B82E-3612E2D06202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB16F07-120B-432D-BD4B-17B781654B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5970" yWindow="2250" windowWidth="21600" windowHeight="11385" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt-diagram" sheetId="2" r:id="rId1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="13"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="13"/>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="13"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="13"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB16F07-120B-432D-BD4B-17B781654B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C504AA65-DE01-4522-91F6-46B117A200E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +122,13 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -155,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -187,6 +194,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -595,7 +603,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="5"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
@@ -683,7 +691,7 @@
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="5"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C504AA65-DE01-4522-91F6-46B117A200E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71A7FE1-7789-4BAE-8AE6-2DAD06ADC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
@@ -619,7 +619,7 @@
       <c r="C5" s="9"/>
       <c r="D5" s="5"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="9"/>
       <c r="G5" s="5"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\aprohirdetes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71A7FE1-7789-4BAE-8AE6-2DAD06ADC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C504AA65-DE01-4522-91F6-46B117A200E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="5"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
@@ -619,7 +619,7 @@
       <c r="C5" s="9"/>
       <c r="D5" s="5"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
